--- a/data/Tyler_CoFL_IsItWorthIt_Proforma.xlsx
+++ b/data/Tyler_CoFL_IsItWorthIt_Proforma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\nate\projects\football\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D625D43A-5B6E-4FDE-978B-17738B5A9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53206753-EB2F-454E-82F3-C2F1E15414EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Cover &amp; Assumptions" sheetId="1" r:id="rId1"/>
@@ -1722,7 +1722,7 @@
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00000%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1857,12 +1857,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2195,9 +2189,6 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2206,6 +2197,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2719,7 +2713,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="78" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="74"/>
@@ -2734,102 +2728,102 @@
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
     </row>
     <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79" t="s">
+      <c r="A14" s="78" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="74"/>
@@ -2862,13 +2856,13 @@
         <v>0.1</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -2878,13 +2872,13 @@
         <v>0.04</v>
       </c>
       <c r="C17" s="7"/>
-      <c r="D17" s="82" t="s">
+      <c r="D17" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -2894,13 +2888,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="82" t="s">
+      <c r="D18" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -2910,13 +2904,13 @@
         <v>5</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -2926,13 +2920,13 @@
         <v>10566</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="82" t="s">
+      <c r="D20" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -2942,13 +2936,13 @@
         <v>1875</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="82" t="s">
+      <c r="D21" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -2958,13 +2952,13 @@
         <v>50000</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="82" t="s">
+      <c r="D22" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -2974,13 +2968,13 @@
         <v>7500</v>
       </c>
       <c r="C23" s="7"/>
-      <c r="D23" s="82" t="s">
+      <c r="D23" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -2990,13 +2984,13 @@
         <v>245000</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="82" t="s">
+      <c r="D24" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -3006,13 +3000,13 @@
         <v>762000</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="82" t="s">
+      <c r="D25" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="81"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -3022,18 +3016,18 @@
         <v>240000</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="82" t="s">
+      <c r="D26" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="78" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="74"/>
@@ -3062,147 +3056,147 @@
       <c r="A31" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="80" t="s">
+      <c r="B34" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="80" t="s">
+      <c r="B35" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="80" t="s">
+      <c r="B36" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="80" t="s">
+      <c r="B37" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="82" t="s">
         <v>67</v>
       </c>
       <c r="C41" s="74"/>
@@ -4173,31 +4167,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="B31:H31"/>
@@ -4206,6 +4175,31 @@
     <mergeCell ref="B34:H34"/>
     <mergeCell ref="B35:H35"/>
     <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4233,7 +4227,7 @@
       <c r="E1" s="75"/>
     </row>
     <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="78" t="s">
         <v>384</v>
       </c>
       <c r="B3" s="74"/>
@@ -4479,7 +4473,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="78" t="s">
         <v>407</v>
       </c>
       <c r="B21" s="74"/>
@@ -7041,7 +7035,7 @@
       <c r="E1" s="75"/>
     </row>
     <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="78" t="s">
         <v>479</v>
       </c>
       <c r="B3" s="74"/>
@@ -7271,7 +7265,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="78" t="s">
         <v>497</v>
       </c>
       <c r="B19" s="74"/>
@@ -8377,7 +8371,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="78" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="74"/>
@@ -8709,7 +8703,7 @@
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="79" t="s">
+      <c r="A25" s="78" t="s">
         <v>106</v>
       </c>
       <c r="B25" s="74"/>
@@ -9831,7 +9825,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="78" t="s">
         <v>124</v>
       </c>
       <c r="B5" s="74"/>
@@ -10116,7 +10110,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="78" t="s">
         <v>152</v>
       </c>
       <c r="B20" s="74"/>
@@ -15246,43 +15240,43 @@
         <v>192</v>
       </c>
       <c r="B7" s="27">
-        <f>SUM(B5:B6)</f>
+        <f t="shared" ref="B7:K7" si="0">SUM(B5:B6)</f>
         <v>414037.5</v>
       </c>
       <c r="C7" s="27">
-        <f>SUM(C5:C6)</f>
+        <f t="shared" si="0"/>
         <v>455441.25000000006</v>
       </c>
       <c r="D7" s="27">
-        <f>SUM(D5:D6)</f>
+        <f t="shared" si="0"/>
         <v>500985.37500000012</v>
       </c>
       <c r="E7" s="27">
-        <f>SUM(E5:E6)</f>
+        <f t="shared" si="0"/>
         <v>551083.91250000021</v>
       </c>
       <c r="F7" s="27">
-        <f>SUM(F5:F6)</f>
+        <f t="shared" si="0"/>
         <v>606192.30375000031</v>
       </c>
       <c r="G7" s="27">
-        <f>SUM(G5:G6)</f>
+        <f t="shared" si="0"/>
         <v>666811.53412500035</v>
       </c>
       <c r="H7" s="27">
-        <f>SUM(H5:H6)</f>
+        <f t="shared" si="0"/>
         <v>733492.6875375004</v>
       </c>
       <c r="I7" s="27">
-        <f>SUM(I5:I6)</f>
+        <f t="shared" si="0"/>
         <v>806841.95629125054</v>
       </c>
       <c r="J7" s="27">
-        <f>SUM(J5:J6)</f>
+        <f t="shared" si="0"/>
         <v>887526.15192037565</v>
       </c>
       <c r="K7" s="27">
-        <f>SUM(K5:K6)</f>
+        <f t="shared" si="0"/>
         <v>976278.7671124133</v>
       </c>
     </row>
@@ -15521,43 +15515,43 @@
         <v>284</v>
       </c>
       <c r="B15" s="28">
-        <f t="shared" ref="B15:K15" si="0">SUM(B11:B14)</f>
+        <f t="shared" ref="B15:K15" si="1">SUM(B11:B14)</f>
         <v>701651.625</v>
       </c>
       <c r="C15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>729717.69</v>
       </c>
       <c r="D15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>758906.39760000003</v>
       </c>
       <c r="E15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>789262.65350400005</v>
       </c>
       <c r="F15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>820833.15964416007</v>
       </c>
       <c r="G15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>853666.48602992645</v>
       </c>
       <c r="H15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>887813.14547112351</v>
       </c>
       <c r="I15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>923325.67128996854</v>
       </c>
       <c r="J15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>960258.69814156741</v>
       </c>
       <c r="K15" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>998669.04606723005</v>
       </c>
     </row>
@@ -15566,43 +15560,43 @@
         <v>301</v>
       </c>
       <c r="B17" s="29">
-        <f t="shared" ref="B17:K17" si="1">B7-B15</f>
+        <f t="shared" ref="B17:K17" si="2">B7-B15</f>
         <v>-287614.125</v>
       </c>
       <c r="C17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-274276.43999999989</v>
       </c>
       <c r="D17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-257921.02259999991</v>
       </c>
       <c r="E17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-238178.74100399984</v>
       </c>
       <c r="F17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-214640.85589415976</v>
       </c>
       <c r="G17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-186854.9519049261</v>
       </c>
       <c r="H17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-154320.45793362311</v>
       </c>
       <c r="I17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-116483.714998718</v>
       </c>
       <c r="J17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-72732.546221191762</v>
       </c>
       <c r="K17" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-22390.278954816749</v>
       </c>
     </row>
@@ -15611,43 +15605,43 @@
         <v>286</v>
       </c>
       <c r="B18" s="26">
-        <f t="shared" ref="B18:K18" si="2">B17/B7</f>
+        <f t="shared" ref="B18:K18" si="3">B17/B7</f>
         <v>-0.69465718684901734</v>
       </c>
       <c r="C18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.60222134029361607</v>
       </c>
       <c r="D18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.51482744900487332</v>
       </c>
       <c r="E18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.43220049724097098</v>
       </c>
       <c r="F18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.35408047011873606</v>
       </c>
       <c r="G18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.28022153538498679</v>
       </c>
       <c r="H18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.21039126981853293</v>
       </c>
       <c r="I18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.14436992782843111</v>
       </c>
       <c r="J18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-8.1949749946880396E-2</v>
       </c>
       <c r="K18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-2.2934309040686766E-2</v>
       </c>
     </row>
@@ -15660,39 +15654,39 @@
         <v>-287614.125</v>
       </c>
       <c r="C19" s="31">
-        <f t="shared" ref="C19:K19" si="3">B19+C17</f>
+        <f t="shared" ref="C19:K19" si="4">B19+C17</f>
         <v>-561890.56499999994</v>
       </c>
       <c r="D19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-819811.58759999985</v>
       </c>
       <c r="E19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1057990.3286039997</v>
       </c>
       <c r="F19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1272631.1844981594</v>
       </c>
       <c r="G19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1459486.1364030857</v>
       </c>
       <c r="H19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1613806.5943367088</v>
       </c>
       <c r="I19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1730290.3093354269</v>
       </c>
       <c r="J19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1803022.8555566187</v>
       </c>
       <c r="K19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1825413.1345114354</v>
       </c>
     </row>
@@ -16950,7 +16944,7 @@
         <v>455441.25000000006</v>
       </c>
       <c r="D7" s="27">
-        <f t="shared" ref="B7:K7" si="0">SUM(D5:D6)</f>
+        <f t="shared" ref="D7:K7" si="0">SUM(D5:D6)</f>
         <v>500985.37500000012</v>
       </c>
       <c r="E7" s="27">
@@ -17734,7 +17728,7 @@
         <v>-122527.84291889396</v>
       </c>
       <c r="I30" s="62">
-        <f t="shared" ref="I29:I37" si="8">I29+H30</f>
+        <f t="shared" ref="I30:I37" si="8">I29+H30</f>
         <v>-408338.04994372168</v>
       </c>
     </row>
@@ -17761,7 +17755,7 @@
         <v>-605413.36610400002</v>
       </c>
       <c r="H31" s="61">
-        <f t="shared" ref="H28:H37" si="10">F31/(1+$H$25)^A31</f>
+        <f t="shared" ref="H31:H37" si="10">F31/(1+$H$25)^A31</f>
         <v>-68707.291861763792</v>
       </c>
       <c r="I31" s="62">
@@ -19056,7 +19050,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="78" t="s">
         <v>314</v>
       </c>
       <c r="B5" s="74"/>
@@ -19245,7 +19239,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="78" t="s">
         <v>336</v>
       </c>
       <c r="B18" s="74"/>
@@ -19258,126 +19252,126 @@
       <c r="A19" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="79" t="s">
         <v>338</v>
       </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="79" t="s">
         <v>340</v>
       </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="79" t="s">
         <v>342</v>
       </c>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="79" t="s">
         <v>344</v>
       </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="79" t="s">
         <v>346</v>
       </c>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="79" t="s">
         <v>348</v>
       </c>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B25" s="80" t="s">
+      <c r="B25" s="79" t="s">
         <v>350</v>
       </c>
-      <c r="C25" s="81"/>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="81"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
     </row>
     <row r="26" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="79" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="79" t="s">
         <v>354</v>
       </c>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="79" t="s">
         <v>356</v>
       </c>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="78" t="s">
         <v>357</v>
       </c>
       <c r="B31" s="74"/>
@@ -19407,12 +19401,12 @@
       <c r="B33" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C33" s="82" t="s">
+      <c r="C33" s="81" t="s">
         <v>363</v>
       </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -19421,12 +19415,12 @@
       <c r="B34" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C34" s="82" t="s">
+      <c r="C34" s="81" t="s">
         <v>365</v>
       </c>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -19435,12 +19429,12 @@
       <c r="B35" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C35" s="82" t="s">
+      <c r="C35" s="81" t="s">
         <v>367</v>
       </c>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -19449,12 +19443,12 @@
       <c r="B36" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C36" s="82" t="s">
+      <c r="C36" s="81" t="s">
         <v>369</v>
       </c>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -19463,12 +19457,12 @@
       <c r="B37" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C37" s="82" t="s">
+      <c r="C37" s="81" t="s">
         <v>371</v>
       </c>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -19477,12 +19471,12 @@
       <c r="B38" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C38" s="82" t="s">
+      <c r="C38" s="81" t="s">
         <v>373</v>
       </c>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -19491,12 +19485,12 @@
       <c r="B39" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C39" s="82" t="s">
+      <c r="C39" s="81" t="s">
         <v>375</v>
       </c>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -19505,12 +19499,12 @@
       <c r="B40" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C40" s="82" t="s">
+      <c r="C40" s="81" t="s">
         <v>377</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
@@ -19519,12 +19513,12 @@
       <c r="B41" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C41" s="82" t="s">
+      <c r="C41" s="81" t="s">
         <v>379</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -19533,12 +19527,12 @@
       <c r="B42" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="C42" s="82" t="s">
+      <c r="C42" s="81" t="s">
         <v>382</v>
       </c>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20500,21 +20494,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="C40:F40"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="C33:F33"/>
@@ -20524,6 +20503,21 @@
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
